--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -103,31 +103,31 @@
     <t>19-jun-26</t>
   </si>
   <si>
-    <t>64.52% (20 de 31)</t>
-  </si>
-  <si>
-    <t>52.63% (20 de 38)</t>
-  </si>
-  <si>
-    <t>78.18% (43 de 55)</t>
-  </si>
-  <si>
-    <t>89.66% (52 de 58)</t>
-  </si>
-  <si>
-    <t>98.33% (59 de 60)</t>
-  </si>
-  <si>
-    <t>95.00% (57 de 60)</t>
-  </si>
-  <si>
-    <t>96.67% (58 de 60)</t>
-  </si>
-  <si>
-    <t>100.00% (12 de 12)</t>
-  </si>
-  <si>
-    <t>60.00% (12 de 20)</t>
+    <t>68.57% (24 de 35)</t>
+  </si>
+  <si>
+    <t>47.62% (20 de 42)</t>
+  </si>
+  <si>
+    <t>71.67% (43 de 60)</t>
+  </si>
+  <si>
+    <t>82.54% (52 de 63)</t>
+  </si>
+  <si>
+    <t>90.77% (59 de 65)</t>
+  </si>
+  <si>
+    <t>87.69% (57 de 65)</t>
+  </si>
+  <si>
+    <t>89.23% (58 de 65)</t>
+  </si>
+  <si>
+    <t>92.31% (12 de 13)</t>
+  </si>
+  <si>
+    <t>66.67% (16 de 24)</t>
   </si>
   <si>
     <t>80.00% (16 de 20)</t>
@@ -151,28 +151,28 @@
     <t>75.00% (9 de 12)</t>
   </si>
   <si>
-    <t>35.48% (11 de 31)</t>
-  </si>
-  <si>
-    <t>47.37% (18 de 38)</t>
-  </si>
-  <si>
-    <t>21.82% (12 de 55)</t>
-  </si>
-  <si>
-    <t>10.34% (6 de 58)</t>
-  </si>
-  <si>
-    <t>1.67% (1 de 60)</t>
-  </si>
-  <si>
-    <t>5.00% (3 de 60)</t>
-  </si>
-  <si>
-    <t>3.33% (2 de 60)</t>
-  </si>
-  <si>
-    <t>0.00% (0 de 12)</t>
+    <t>31.43% (11 de 35)</t>
+  </si>
+  <si>
+    <t>52.38% (22 de 42)</t>
+  </si>
+  <si>
+    <t>28.33% (17 de 60)</t>
+  </si>
+  <si>
+    <t>17.46% (11 de 63)</t>
+  </si>
+  <si>
+    <t>9.23% (6 de 65)</t>
+  </si>
+  <si>
+    <t>12.31% (8 de 65)</t>
+  </si>
+  <si>
+    <t>10.77% (7 de 65)</t>
+  </si>
+  <si>
+    <t>7.69% (1 de 13)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Semana</t>
   </si>
@@ -103,6 +103,9 @@
     <t>19-jun-26</t>
   </si>
   <si>
+    <t>23-jun-26</t>
+  </si>
+  <si>
     <t>68.57% (24 de 35)</t>
   </si>
   <si>
@@ -124,7 +127,7 @@
     <t>89.23% (58 de 65)</t>
   </si>
   <si>
-    <t>92.31% (12 de 13)</t>
+    <t>92.31% (24 de 26)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -148,7 +151,7 @@
     <t>50.00% (29 de 58)</t>
   </si>
   <si>
-    <t>75.00% (9 de 12)</t>
+    <t>79.17% (19 de 24)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -172,7 +175,7 @@
     <t>10.77% (7 de 65)</t>
   </si>
   <si>
-    <t>7.69% (1 de 13)</t>
+    <t>7.69% (2 de 26)</t>
   </si>
 </sst>
 </file>
@@ -538,13 +541,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -558,13 +561,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -578,13 +581,13 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -598,13 +601,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -618,13 +621,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -638,13 +641,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -658,13 +661,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -675,16 +678,16 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -103,7 +103,7 @@
     <t>19-jun-26</t>
   </si>
   <si>
-    <t>23-jun-26</t>
+    <t>24-jun-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -127,7 +127,7 @@
     <t>89.23% (58 de 65)</t>
   </si>
   <si>
-    <t>92.31% (24 de 26)</t>
+    <t>92.31% (36 de 39)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -151,7 +151,7 @@
     <t>50.00% (29 de 58)</t>
   </si>
   <si>
-    <t>79.17% (19 de 24)</t>
+    <t>75.00% (27 de 36)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -175,7 +175,7 @@
     <t>10.77% (7 de 65)</t>
   </si>
   <si>
-    <t>7.69% (2 de 26)</t>
+    <t>7.69% (3 de 39)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Semana</t>
   </si>
@@ -121,9 +121,6 @@
     <t>90.77% (59 de 65)</t>
   </si>
   <si>
-    <t>87.69% (57 de 65)</t>
-  </si>
-  <si>
     <t>89.23% (58 de 65)</t>
   </si>
   <si>
@@ -145,7 +142,7 @@
     <t>67.80% (40 de 59)</t>
   </si>
   <si>
-    <t>68.42% (39 de 57)</t>
+    <t>67.24% (39 de 58)</t>
   </si>
   <si>
     <t>50.00% (29 de 58)</t>
@@ -167,9 +164,6 @@
   </si>
   <si>
     <t>9.23% (6 de 65)</t>
-  </si>
-  <si>
-    <t>12.31% (8 de 65)</t>
   </si>
   <si>
     <t>10.77% (7 de 65)</t>
@@ -544,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -564,10 +558,10 @@
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -584,10 +578,10 @@
         <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -604,10 +598,10 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -624,10 +618,10 @@
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -644,10 +638,10 @@
         <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -661,13 +655,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -681,13 +675,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -103,7 +103,7 @@
     <t>19-jun-26</t>
   </si>
   <si>
-    <t>24-jun-26</t>
+    <t>25-jun-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -124,7 +124,7 @@
     <t>89.23% (58 de 65)</t>
   </si>
   <si>
-    <t>92.31% (36 de 39)</t>
+    <t>92.31% (48 de 52)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -148,7 +148,7 @@
     <t>50.00% (29 de 58)</t>
   </si>
   <si>
-    <t>75.00% (27 de 36)</t>
+    <t>75.00% (36 de 48)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -169,7 +169,7 @@
     <t>10.77% (7 de 65)</t>
   </si>
   <si>
-    <t>7.69% (3 de 39)</t>
+    <t>7.69% (4 de 52)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -103,7 +103,7 @@
     <t>19-jun-26</t>
   </si>
   <si>
-    <t>25-jun-26</t>
+    <t>26-jun-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -124,7 +124,7 @@
     <t>89.23% (58 de 65)</t>
   </si>
   <si>
-    <t>92.31% (48 de 52)</t>
+    <t>92.31% (60 de 65)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -148,7 +148,7 @@
     <t>50.00% (29 de 58)</t>
   </si>
   <si>
-    <t>75.00% (36 de 48)</t>
+    <t>75.00% (45 de 60)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -169,7 +169,7 @@
     <t>10.77% (7 de 65)</t>
   </si>
   <si>
-    <t>7.69% (4 de 52)</t>
+    <t>7.69% (5 de 65)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>Semana</t>
   </si>
@@ -58,6 +58,9 @@
     <t>Semana 26</t>
   </si>
   <si>
+    <t>Semana 27</t>
+  </si>
+  <si>
     <t>05-may-26</t>
   </si>
   <si>
@@ -82,6 +85,9 @@
     <t>22-jun-26</t>
   </si>
   <si>
+    <t>29-jun-26</t>
+  </si>
+  <si>
     <t>08-may-26</t>
   </si>
   <si>
@@ -127,6 +133,9 @@
     <t>92.31% (60 de 65)</t>
   </si>
   <si>
+    <t>84.62% (11 de 13)</t>
+  </si>
+  <si>
     <t>66.67% (16 de 24)</t>
   </si>
   <si>
@@ -151,6 +160,9 @@
     <t>75.00% (45 de 60)</t>
   </si>
   <si>
+    <t>72.73% (8 de 11)</t>
+  </si>
+  <si>
     <t>31.43% (11 de 35)</t>
   </si>
   <si>
@@ -170,6 +182,9 @@
   </si>
   <si>
     <t>7.69% (5 de 65)</t>
+  </si>
+  <si>
+    <t>15.38% (2 de 13)</t>
   </si>
 </sst>
 </file>
@@ -501,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -529,19 +544,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -549,19 +564,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -569,19 +584,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -589,19 +604,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -609,19 +624,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -629,19 +644,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -649,19 +664,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -669,19 +684,39 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Semana</t>
   </si>
@@ -112,6 +112,9 @@
     <t>26-jun-26</t>
   </si>
   <si>
+    <t>30-jun-26</t>
+  </si>
+  <si>
     <t>68.57% (24 de 35)</t>
   </si>
   <si>
@@ -133,7 +136,7 @@
     <t>92.31% (60 de 65)</t>
   </si>
   <si>
-    <t>84.62% (11 de 13)</t>
+    <t>80.77% (21 de 26)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -160,7 +163,7 @@
     <t>75.00% (45 de 60)</t>
   </si>
   <si>
-    <t>72.73% (8 de 11)</t>
+    <t>80.95% (17 de 21)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -184,7 +187,7 @@
     <t>7.69% (5 de 65)</t>
   </si>
   <si>
-    <t>15.38% (2 de 13)</t>
+    <t>19.23% (5 de 26)</t>
   </si>
 </sst>
 </file>
@@ -550,13 +553,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -570,13 +573,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -590,13 +593,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -610,13 +613,13 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -630,13 +633,13 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -650,13 +653,13 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -670,13 +673,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -690,13 +693,13 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -707,16 +710,16 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -112,7 +112,7 @@
     <t>26-jun-26</t>
   </si>
   <si>
-    <t>30-jun-26</t>
+    <t>01-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -136,7 +136,7 @@
     <t>92.31% (60 de 65)</t>
   </si>
   <si>
-    <t>80.77% (21 de 26)</t>
+    <t>76.92% (30 de 39)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -163,7 +163,7 @@
     <t>75.00% (45 de 60)</t>
   </si>
   <si>
-    <t>80.95% (17 de 21)</t>
+    <t>73.33% (22 de 30)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -187,7 +187,7 @@
     <t>7.69% (5 de 65)</t>
   </si>
   <si>
-    <t>19.23% (5 de 26)</t>
+    <t>23.08% (9 de 39)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -136,7 +136,7 @@
     <t>92.31% (60 de 65)</t>
   </si>
   <si>
-    <t>76.92% (30 de 39)</t>
+    <t>82.05% (32 de 39)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -163,7 +163,7 @@
     <t>75.00% (45 de 60)</t>
   </si>
   <si>
-    <t>73.33% (22 de 30)</t>
+    <t>68.75% (22 de 32)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -187,7 +187,7 @@
     <t>7.69% (5 de 65)</t>
   </si>
   <si>
-    <t>23.08% (9 de 39)</t>
+    <t>17.95% (7 de 39)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -112,7 +112,7 @@
     <t>26-jun-26</t>
   </si>
   <si>
-    <t>01-jul-26</t>
+    <t>02-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -136,7 +136,7 @@
     <t>92.31% (60 de 65)</t>
   </si>
   <si>
-    <t>82.05% (32 de 39)</t>
+    <t>82.69% (43 de 52)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -163,7 +163,7 @@
     <t>75.00% (45 de 60)</t>
   </si>
   <si>
-    <t>68.75% (22 de 32)</t>
+    <t>72.09% (31 de 43)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -187,7 +187,7 @@
     <t>7.69% (5 de 65)</t>
   </si>
   <si>
-    <t>17.95% (7 de 39)</t>
+    <t>17.31% (9 de 52)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -112,7 +112,7 @@
     <t>26-jun-26</t>
   </si>
   <si>
-    <t>02-jul-26</t>
+    <t>03-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -136,7 +136,7 @@
     <t>92.31% (60 de 65)</t>
   </si>
   <si>
-    <t>82.69% (43 de 52)</t>
+    <t>84.62% (55 de 65)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -163,7 +163,7 @@
     <t>75.00% (45 de 60)</t>
   </si>
   <si>
-    <t>72.09% (31 de 43)</t>
+    <t>76.36% (42 de 55)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -187,7 +187,7 @@
     <t>7.69% (5 de 65)</t>
   </si>
   <si>
-    <t>17.31% (9 de 52)</t>
+    <t>15.38% (10 de 65)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t>Semana</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Semana 27</t>
   </si>
   <si>
+    <t>Semana 28</t>
+  </si>
+  <si>
     <t>05-may-26</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>29-jun-26</t>
   </si>
   <si>
+    <t>06-jul-26</t>
+  </si>
+  <si>
     <t>08-may-26</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t>84.62% (55 de 65)</t>
   </si>
   <si>
+    <t>92.31% (12 de 13)</t>
+  </si>
+  <si>
     <t>66.67% (16 de 24)</t>
   </si>
   <si>
@@ -166,6 +175,9 @@
     <t>76.36% (42 de 55)</t>
   </si>
   <si>
+    <t>83.33% (10 de 12)</t>
+  </si>
+  <si>
     <t>31.43% (11 de 35)</t>
   </si>
   <si>
@@ -188,6 +200,9 @@
   </si>
   <si>
     <t>15.38% (10 de 65)</t>
+  </si>
+  <si>
+    <t>7.69% (1 de 13)</t>
   </si>
 </sst>
 </file>
@@ -519,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -547,19 +562,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -567,19 +582,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -587,19 +602,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -607,19 +622,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -627,19 +642,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -647,19 +662,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -667,19 +682,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -687,19 +702,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -707,19 +722,39 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>Semana</t>
   </si>
@@ -121,6 +121,9 @@
     <t>03-jul-26</t>
   </si>
   <si>
+    <t>07-jul-26</t>
+  </si>
+  <si>
     <t>68.57% (24 de 35)</t>
   </si>
   <si>
@@ -145,7 +148,7 @@
     <t>84.62% (55 de 65)</t>
   </si>
   <si>
-    <t>92.31% (12 de 13)</t>
+    <t>88.46% (23 de 26)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -175,7 +178,7 @@
     <t>76.36% (42 de 55)</t>
   </si>
   <si>
-    <t>83.33% (10 de 12)</t>
+    <t>86.96% (20 de 23)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -202,7 +205,7 @@
     <t>15.38% (10 de 65)</t>
   </si>
   <si>
-    <t>7.69% (1 de 13)</t>
+    <t>11.54% (3 de 26)</t>
   </si>
 </sst>
 </file>
@@ -568,13 +571,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -588,13 +591,13 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -608,13 +611,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -628,13 +631,13 @@
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -648,13 +651,13 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -668,13 +671,13 @@
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -688,13 +691,13 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -708,13 +711,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -728,13 +731,13 @@
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -745,16 +748,16 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -121,7 +121,7 @@
     <t>03-jul-26</t>
   </si>
   <si>
-    <t>07-jul-26</t>
+    <t>08-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -148,7 +148,7 @@
     <t>84.62% (55 de 65)</t>
   </si>
   <si>
-    <t>88.46% (23 de 26)</t>
+    <t>84.62% (33 de 39)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -178,7 +178,7 @@
     <t>76.36% (42 de 55)</t>
   </si>
   <si>
-    <t>86.96% (20 de 23)</t>
+    <t>78.79% (26 de 33)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -205,7 +205,7 @@
     <t>15.38% (10 de 65)</t>
   </si>
   <si>
-    <t>11.54% (3 de 26)</t>
+    <t>15.38% (6 de 39)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -121,7 +121,7 @@
     <t>03-jul-26</t>
   </si>
   <si>
-    <t>08-jul-26</t>
+    <t>09-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -148,7 +148,7 @@
     <t>84.62% (55 de 65)</t>
   </si>
   <si>
-    <t>84.62% (33 de 39)</t>
+    <t>86.54% (45 de 52)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -178,7 +178,7 @@
     <t>76.36% (42 de 55)</t>
   </si>
   <si>
-    <t>78.79% (26 de 33)</t>
+    <t>77.78% (35 de 45)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -205,7 +205,7 @@
     <t>15.38% (10 de 65)</t>
   </si>
   <si>
-    <t>15.38% (6 de 39)</t>
+    <t>13.46% (7 de 52)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -148,7 +148,7 @@
     <t>84.62% (55 de 65)</t>
   </si>
   <si>
-    <t>86.54% (45 de 52)</t>
+    <t>88.46% (46 de 52)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -178,7 +178,7 @@
     <t>76.36% (42 de 55)</t>
   </si>
   <si>
-    <t>77.78% (35 de 45)</t>
+    <t>76.09% (35 de 46)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -205,7 +205,7 @@
     <t>15.38% (10 de 65)</t>
   </si>
   <si>
-    <t>13.46% (7 de 52)</t>
+    <t>11.54% (6 de 52)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -121,7 +121,7 @@
     <t>03-jul-26</t>
   </si>
   <si>
-    <t>09-jul-26</t>
+    <t>10-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
@@ -148,7 +148,7 @@
     <t>84.62% (55 de 65)</t>
   </si>
   <si>
-    <t>88.46% (46 de 52)</t>
+    <t>87.69% (57 de 65)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -178,7 +178,7 @@
     <t>76.36% (42 de 55)</t>
   </si>
   <si>
-    <t>76.09% (35 de 46)</t>
+    <t>73.68% (42 de 57)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -205,7 +205,7 @@
     <t>15.38% (10 de 65)</t>
   </si>
   <si>
-    <t>11.54% (6 de 52)</t>
+    <t>12.31% (8 de 65)</t>
   </si>
 </sst>
 </file>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>Semana</t>
   </si>
@@ -64,6 +64,9 @@
     <t>Semana 28</t>
   </si>
   <si>
+    <t>Semana 29</t>
+  </si>
+  <si>
     <t>05-may-26</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>06-jul-26</t>
   </si>
   <si>
+    <t>13-jul-26</t>
+  </si>
+  <si>
     <t>08-may-26</t>
   </si>
   <si>
@@ -151,6 +157,9 @@
     <t>87.69% (57 de 65)</t>
   </si>
   <si>
+    <t>84.62% (11 de 13)</t>
+  </si>
+  <si>
     <t>66.67% (16 de 24)</t>
   </si>
   <si>
@@ -181,6 +190,9 @@
     <t>73.68% (42 de 57)</t>
   </si>
   <si>
+    <t>81.82% (9 de 11)</t>
+  </si>
+  <si>
     <t>31.43% (11 de 35)</t>
   </si>
   <si>
@@ -206,6 +218,9 @@
   </si>
   <si>
     <t>12.31% (8 de 65)</t>
+  </si>
+  <si>
+    <t>15.38% (2 de 13)</t>
   </si>
 </sst>
 </file>
@@ -537,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -565,19 +580,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -585,19 +600,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -605,19 +620,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -625,19 +640,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -645,19 +660,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -665,19 +680,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -685,19 +700,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -705,19 +720,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -725,19 +740,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -745,19 +760,39 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>Semana</t>
   </si>
@@ -130,6 +130,9 @@
     <t>10-jul-26</t>
   </si>
   <si>
+    <t>14-jul-26</t>
+  </si>
+  <si>
     <t>68.57% (24 de 35)</t>
   </si>
   <si>
@@ -157,7 +160,7 @@
     <t>87.69% (57 de 65)</t>
   </si>
   <si>
-    <t>84.62% (11 de 13)</t>
+    <t>88.46% (23 de 26)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
@@ -190,7 +193,7 @@
     <t>73.68% (42 de 57)</t>
   </si>
   <si>
-    <t>81.82% (9 de 11)</t>
+    <t>86.96% (20 de 23)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
@@ -220,7 +223,7 @@
     <t>12.31% (8 de 65)</t>
   </si>
   <si>
-    <t>15.38% (2 de 13)</t>
+    <t>11.54% (3 de 26)</t>
   </si>
 </sst>
 </file>
@@ -586,13 +589,13 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -606,13 +609,13 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -626,13 +629,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -646,13 +649,13 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -666,13 +669,13 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -686,13 +689,13 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -706,13 +709,13 @@
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -726,13 +729,13 @@
         <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -746,13 +749,13 @@
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -766,13 +769,13 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -783,16 +786,16 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/asistencias/historico_semanal.xlsx
+++ b/asistencias/historico_semanal.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
   <si>
     <t>Semana</t>
   </si>
   <si>
+    <t>Año</t>
+  </si>
+  <si>
     <t>Fecha Inicio</t>
   </si>
   <si>
@@ -67,6 +70,12 @@
     <t>Semana 29</t>
   </si>
   <si>
+    <t>Semana 30</t>
+  </si>
+  <si>
+    <t>Semana 31</t>
+  </si>
+  <si>
     <t>05-may-26</t>
   </si>
   <si>
@@ -100,6 +109,12 @@
     <t>13-jul-26</t>
   </si>
   <si>
+    <t>20-jul-26</t>
+  </si>
+  <si>
+    <t>27-jul-26</t>
+  </si>
+  <si>
     <t>08-may-26</t>
   </si>
   <si>
@@ -130,13 +145,19 @@
     <t>10-jul-26</t>
   </si>
   <si>
-    <t>14-jul-26</t>
+    <t>17-jul-26</t>
+  </si>
+  <si>
+    <t>24-jul-26</t>
+  </si>
+  <si>
+    <t>31-jul-26</t>
   </si>
   <si>
     <t>68.57% (24 de 35)</t>
   </si>
   <si>
-    <t>47.62% (20 de 42)</t>
+    <t>48.39% (15 de 31)</t>
   </si>
   <si>
     <t>71.67% (43 de 60)</t>
@@ -160,13 +181,13 @@
     <t>87.69% (57 de 65)</t>
   </si>
   <si>
-    <t>88.46% (23 de 26)</t>
+    <t>86.15% (56 de 65)</t>
   </si>
   <si>
     <t>66.67% (16 de 24)</t>
   </si>
   <si>
-    <t>80.00% (16 de 20)</t>
+    <t>86.67% (13 de 15)</t>
   </si>
   <si>
     <t>65.12% (28 de 43)</t>
@@ -193,13 +214,16 @@
     <t>73.68% (42 de 57)</t>
   </si>
   <si>
-    <t>86.96% (20 de 23)</t>
+    <t>78.57% (44 de 56)</t>
+  </si>
+  <si>
+    <t>64.91% (37 de 57)</t>
   </si>
   <si>
     <t>31.43% (11 de 35)</t>
   </si>
   <si>
-    <t>52.38% (22 de 42)</t>
+    <t>51.61% (16 de 31)</t>
   </si>
   <si>
     <t>28.33% (17 de 60)</t>
@@ -223,7 +247,7 @@
     <t>12.31% (8 de 65)</t>
   </si>
   <si>
-    <t>11.54% (3 de 26)</t>
+    <t>13.85% (9 de 65)</t>
   </si>
 </sst>
 </file>
@@ -555,10 +579,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -577,225 +601,307 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>2026</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2026</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>2026</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>2026</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>2026</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>2026</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>2026</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>2026</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>2026</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>2026</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B12">
+        <v>2026</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B13">
+        <v>2026</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B14">
+        <v>2026</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="F14" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>69</v>
+      <c r="G14" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
